--- a/se/data/01_コピーチャージ_カウンター明細_2026年9月.xlsx
+++ b/se/data/01_コピーチャージ_カウンター明細_2026年9月.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>サンプル歯科株式会社</t>
+          <t>サンプル歯科医院</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1332,12 +1332,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>K121</t>
+          <t>K129</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>サンプル製菓（本社）</t>
+          <t>サンプル衣料株式会社（倉庫）</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1649,6 +1649,7 @@
         <v>902</v>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
@@ -1743,7 +1744,6 @@
           <t>567</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
